--- a/印象文集/视频籍录.xlsx
+++ b/印象文集/视频籍录.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="172">
   <si>
     <t>目录</t>
   </si>
@@ -733,6 +733,40 @@
   </si>
   <si>
     <t>[2021]天桥上的魔术师</t>
+  </si>
+  <si>
+    <t>[2025]疯狂动物城2.Zootopia 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025/11/26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2016]爱宠大机密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025/11/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2010]苍穹之昴</t>
+  </si>
+  <si>
+    <t>历史</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2004]花与爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2022]Hunt.韩国</t>
+  </si>
+  <si>
+    <t>[2004]南方与北方.North.And.South</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -939,7 +973,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -998,6 +1032,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1324,14 +1379,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
     <col min="2" max="2" width="15.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="59.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.75" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.25" style="25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.875" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
@@ -1357,196 +1412,200 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="E2" s="19"/>
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="25"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="7"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="11"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="25"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="7"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="25"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="7"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="25"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="7"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="25"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="25"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="7"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="25"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="7"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="11" t="s">
+        <v>163</v>
+      </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="19" t="s">
+        <v>164</v>
+      </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="25"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="7"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="25"/>
-      <c r="B12" s="27" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="25"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="7"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="25"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="7"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="25"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="25"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="11"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="25"/>
-      <c r="B17" s="27" t="s">
+      <c r="A17" s="32"/>
+      <c r="B17" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="25"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="11"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="19"/>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="25"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="11"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
+      <c r="E19" s="19"/>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="25"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="11"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="19"/>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="25"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="11"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="25"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="11"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="25"/>
-      <c r="B23" s="27" t="s">
+      <c r="A23" s="32"/>
+      <c r="B23" s="34" t="s">
         <v>126</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="19"/>
       <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="25"/>
-      <c r="B24" s="28"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="11" t="s">
         <v>160</v>
       </c>
@@ -1557,47 +1616,47 @@
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="25"/>
-      <c r="B25" s="28"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="11"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="25"/>
-      <c r="B26" s="28"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="11"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="25"/>
-      <c r="B27" s="29"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="11"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="25"/>
-      <c r="B28" s="27" t="s">
+      <c r="A28" s="32"/>
+      <c r="B28" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="7"/>
+      <c r="C28" s="11"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="E28" s="19"/>
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="25"/>
-      <c r="B29" s="28"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="11" t="s">
         <v>128</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="19" t="s">
         <v>129</v>
       </c>
       <c r="F29" s="8" t="s">
@@ -1605,891 +1664,923 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="25"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="7"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
+      <c r="E30" s="19"/>
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="25"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="7"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="11"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="25"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="8"/>
+      <c r="E32" s="19"/>
       <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="26"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="11" t="s">
+        <v>165</v>
+      </c>
       <c r="D33" s="7"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="19" t="s">
+        <v>166</v>
+      </c>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="32"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="8"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="33"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="8"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="25"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="25"/>
       <c r="B36" s="6"/>
-      <c r="C36" s="11" t="s">
-        <v>71</v>
-      </c>
+      <c r="C36" s="11"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="25"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="6"/>
       <c r="C37" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D37" s="7"/>
-      <c r="E37" s="8"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="25"/>
+      <c r="A38" s="32"/>
       <c r="B38" s="6"/>
       <c r="C38" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D38" s="7"/>
-      <c r="E38" s="8"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="25"/>
+      <c r="A39" s="32"/>
       <c r="B39" s="6"/>
       <c r="C39" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="8"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="25"/>
+      <c r="A40" s="32"/>
       <c r="B40" s="6"/>
       <c r="C40" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D40" s="7"/>
-      <c r="E40" s="8"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="25"/>
+      <c r="A41" s="32"/>
       <c r="B41" s="6"/>
       <c r="C41" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
+      <c r="E41" s="19"/>
       <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="25"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="6"/>
       <c r="C42" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
+      <c r="E42" s="19"/>
       <c r="F42" s="8"/>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="25"/>
+      <c r="A43" s="32"/>
       <c r="B43" s="6"/>
       <c r="C43" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D43" s="7"/>
-      <c r="E43" s="8"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="8"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="25"/>
+      <c r="A44" s="32"/>
       <c r="B44" s="6"/>
       <c r="C44" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D44" s="7"/>
-      <c r="E44" s="8"/>
+      <c r="E44" s="19"/>
       <c r="F44" s="8"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="25"/>
+      <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="11" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="D45" s="7"/>
-      <c r="E45" s="8" t="s">
-        <v>153</v>
-      </c>
+      <c r="E45" s="19"/>
       <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="25"/>
+      <c r="A46" s="32"/>
       <c r="B46" s="6"/>
       <c r="C46" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="E46" s="19"/>
       <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="25"/>
+      <c r="A47" s="32"/>
       <c r="B47" s="6"/>
       <c r="C47" s="11" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="D47" s="7"/>
-      <c r="E47" s="8"/>
+      <c r="E47" s="19" t="s">
+        <v>153</v>
+      </c>
       <c r="F47" s="8"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="25"/>
+      <c r="A48" s="32"/>
       <c r="B48" s="6"/>
       <c r="C48" s="11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="E48" s="19"/>
       <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="25"/>
+      <c r="A49" s="32"/>
       <c r="B49" s="6"/>
       <c r="C49" s="11" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D49" s="7"/>
-      <c r="E49" s="8"/>
+      <c r="E49" s="19"/>
       <c r="F49" s="8"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="25"/>
+      <c r="A50" s="32"/>
       <c r="B50" s="6"/>
       <c r="C50" s="11" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D50" s="7"/>
-      <c r="E50" s="8"/>
+      <c r="E50" s="19"/>
       <c r="F50" s="8"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="25"/>
+      <c r="A51" s="32"/>
       <c r="B51" s="6"/>
       <c r="C51" s="11" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="E51" s="19"/>
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="25"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="6"/>
       <c r="C52" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D52" s="7"/>
-      <c r="E52" s="8"/>
+      <c r="E52" s="19"/>
       <c r="F52" s="8"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="25"/>
+      <c r="A53" s="32"/>
       <c r="B53" s="6"/>
       <c r="C53" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D53" s="7"/>
-      <c r="E53" s="8"/>
+      <c r="E53" s="19"/>
       <c r="F53" s="8"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="25"/>
+      <c r="A54" s="32"/>
       <c r="B54" s="6"/>
       <c r="C54" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D54" s="7"/>
-      <c r="E54" s="8"/>
+      <c r="E54" s="19"/>
       <c r="F54" s="8"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="25"/>
+      <c r="A55" s="32"/>
       <c r="B55" s="6"/>
       <c r="C55" s="11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D55" s="7"/>
-      <c r="E55" s="8"/>
+      <c r="E55" s="19"/>
       <c r="F55" s="8"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="25"/>
+      <c r="A56" s="32"/>
       <c r="B56" s="6"/>
       <c r="C56" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
+      <c r="E56" s="19"/>
       <c r="F56" s="8"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="25"/>
+      <c r="A57" s="32"/>
       <c r="B57" s="6"/>
       <c r="C57" s="11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D57" s="7"/>
-      <c r="E57" s="8"/>
+      <c r="E57" s="19"/>
       <c r="F57" s="8"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="25"/>
+      <c r="A58" s="32"/>
       <c r="B58" s="6"/>
       <c r="C58" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="8"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="32"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="32"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="25"/>
-      <c r="B59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="25"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="7"/>
       <c r="D60" s="7"/>
-      <c r="E60" s="8"/>
+      <c r="E60" s="19"/>
       <c r="F60" s="8"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="25"/>
+      <c r="A61" s="32"/>
       <c r="B61" s="6"/>
-      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
+      <c r="E61" s="19"/>
       <c r="F61" s="8"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="25"/>
+      <c r="A62" s="32"/>
       <c r="B62" s="6"/>
-      <c r="C62" s="7"/>
+      <c r="C62" s="11"/>
       <c r="D62" s="7"/>
-      <c r="E62" s="8"/>
+      <c r="E62" s="19"/>
       <c r="F62" s="8"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="25"/>
+      <c r="A63" s="32"/>
       <c r="B63" s="6"/>
-      <c r="C63" s="7"/>
+      <c r="C63" s="11"/>
       <c r="D63" s="7"/>
-      <c r="E63" s="8"/>
+      <c r="E63" s="19"/>
       <c r="F63" s="8"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="25"/>
+      <c r="A64" s="32"/>
       <c r="B64" s="6"/>
-      <c r="C64" s="7"/>
+      <c r="C64" s="11"/>
       <c r="D64" s="7"/>
-      <c r="E64" s="8"/>
+      <c r="E64" s="19"/>
       <c r="F64" s="8"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="25"/>
+      <c r="A65" s="32"/>
       <c r="B65" s="6"/>
-      <c r="C65" s="7"/>
+      <c r="C65" s="11"/>
       <c r="D65" s="7"/>
-      <c r="E65" s="8"/>
+      <c r="E65" s="19"/>
       <c r="F65" s="8"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="25"/>
+      <c r="A66" s="32"/>
       <c r="B66" s="6"/>
-      <c r="C66" s="7"/>
+      <c r="C66" s="11"/>
       <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
+      <c r="E66" s="19"/>
       <c r="F66" s="8"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="25"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="6"/>
-      <c r="C67" s="7"/>
+      <c r="C67" s="11"/>
       <c r="D67" s="7"/>
-      <c r="E67" s="8"/>
+      <c r="E67" s="19"/>
       <c r="F67" s="8"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="25"/>
+      <c r="A68" s="32"/>
       <c r="B68" s="6"/>
-      <c r="C68" s="7"/>
+      <c r="C68" s="11"/>
       <c r="D68" s="7"/>
-      <c r="E68" s="8"/>
+      <c r="E68" s="19"/>
       <c r="F68" s="8"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="25"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="6"/>
-      <c r="C69" s="7"/>
+      <c r="C69" s="11"/>
       <c r="D69" s="7"/>
-      <c r="E69" s="8"/>
+      <c r="E69" s="19"/>
       <c r="F69" s="8"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="25"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="6"/>
-      <c r="C70" s="7"/>
+      <c r="C70" s="11"/>
       <c r="D70" s="7"/>
-      <c r="E70" s="8"/>
+      <c r="E70" s="19"/>
       <c r="F70" s="8"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="25"/>
+      <c r="A71" s="32"/>
       <c r="B71" s="6"/>
-      <c r="C71" s="7"/>
+      <c r="C71" s="11"/>
       <c r="D71" s="7"/>
-      <c r="E71" s="8"/>
+      <c r="E71" s="19"/>
       <c r="F71" s="8"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="25"/>
+      <c r="A72" s="32"/>
       <c r="B72" s="6"/>
-      <c r="C72" s="7"/>
+      <c r="C72" s="11"/>
       <c r="D72" s="7"/>
-      <c r="E72" s="8"/>
+      <c r="E72" s="19"/>
       <c r="F72" s="8"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="25"/>
+      <c r="A73" s="32"/>
       <c r="B73" s="6"/>
-      <c r="C73" s="7"/>
+      <c r="C73" s="11"/>
       <c r="D73" s="7"/>
-      <c r="E73" s="8"/>
+      <c r="E73" s="19"/>
       <c r="F73" s="8"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="25"/>
+      <c r="A74" s="32"/>
       <c r="B74" s="6"/>
-      <c r="C74" s="7"/>
+      <c r="C74" s="11"/>
       <c r="D74" s="7"/>
-      <c r="E74" s="8"/>
+      <c r="E74" s="19"/>
       <c r="F74" s="8"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="25"/>
+      <c r="A75" s="32"/>
       <c r="B75" s="6"/>
-      <c r="C75" s="7"/>
+      <c r="C75" s="11"/>
       <c r="D75" s="7"/>
-      <c r="E75" s="8"/>
+      <c r="E75" s="19"/>
       <c r="F75" s="8"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="25"/>
+      <c r="A76" s="32"/>
       <c r="B76" s="6"/>
-      <c r="C76" s="7"/>
+      <c r="C76" s="11"/>
       <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+      <c r="E76" s="19"/>
       <c r="F76" s="8"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="25"/>
+      <c r="A77" s="32"/>
       <c r="B77" s="6"/>
-      <c r="C77" s="7"/>
+      <c r="C77" s="11"/>
       <c r="D77" s="7"/>
-      <c r="E77" s="8"/>
+      <c r="E77" s="19"/>
       <c r="F77" s="8"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="25"/>
+      <c r="A78" s="32"/>
       <c r="B78" s="6"/>
-      <c r="C78" s="7"/>
+      <c r="C78" s="11"/>
       <c r="D78" s="7"/>
-      <c r="E78" s="8"/>
+      <c r="E78" s="19"/>
       <c r="F78" s="8"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="25"/>
+      <c r="A79" s="32"/>
       <c r="B79" s="6"/>
-      <c r="C79" s="7"/>
+      <c r="C79" s="11"/>
       <c r="D79" s="7"/>
-      <c r="E79" s="8"/>
+      <c r="E79" s="19"/>
       <c r="F79" s="8"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="25"/>
+      <c r="A80" s="32"/>
       <c r="B80" s="6"/>
-      <c r="C80" s="7"/>
+      <c r="C80" s="11"/>
       <c r="D80" s="7"/>
-      <c r="E80" s="8"/>
+      <c r="E80" s="19"/>
       <c r="F80" s="8"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="26"/>
+      <c r="A81" s="32"/>
       <c r="B81" s="6"/>
-      <c r="C81" s="7"/>
+      <c r="C81" s="11"/>
       <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
+      <c r="E81" s="19"/>
       <c r="F81" s="8"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="32"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="8"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="33"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="20"/>
-      <c r="B83" s="22" t="s">
+      <c r="B84" s="6"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="8"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="27"/>
+      <c r="B85" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="20"/>
-      <c r="B84" s="22"/>
-      <c r="C84" s="5" t="s">
+      <c r="C85" s="22"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="5"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="27"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="20"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="5" t="s">
+      <c r="D86" s="5"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="5"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="27"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="20"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="5" t="s">
+      <c r="D87" s="5"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="5"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="27"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="20"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="5" t="s">
+      <c r="D88" s="5"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="5"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="27"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="20"/>
-      <c r="B88" s="22"/>
-      <c r="C88" s="5" t="s">
+      <c r="D89" s="5"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="5"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="27"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" s="20"/>
-      <c r="B89" s="22"/>
-      <c r="C89" s="5" t="s">
+      <c r="D90" s="5"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="5"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="27"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" s="20"/>
-      <c r="B90" s="22"/>
-      <c r="C90" s="5" t="s">
+      <c r="D91" s="5"/>
+      <c r="E91" s="23"/>
+      <c r="F91" s="5"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="27"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" s="20"/>
-      <c r="B91" s="22"/>
-      <c r="C91" s="5" t="s">
+      <c r="D92" s="5"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="5"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="27"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="20"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="5" t="s">
+      <c r="D93" s="5"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="5"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="27"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" s="20"/>
-      <c r="B93" s="22"/>
-      <c r="C93" s="5" t="s">
+      <c r="D94" s="5"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="5"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="27"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" s="20"/>
-      <c r="B94" s="22"/>
-      <c r="C94" s="5" t="s">
+      <c r="D95" s="5"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="5"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="27"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" s="20"/>
-      <c r="B95" s="22"/>
-      <c r="C95" s="5" t="s">
+      <c r="D96" s="5"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="5"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="27"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="20"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="5" t="s">
+      <c r="D97" s="5"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="5"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="27"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" s="20"/>
-      <c r="B97" s="22"/>
-      <c r="C97" s="5" t="s">
+      <c r="D98" s="5"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="5"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="27"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" s="20"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="5" t="s">
+      <c r="D99" s="5"/>
+      <c r="E99" s="23"/>
+      <c r="F99" s="5"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="27"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99" s="20"/>
-      <c r="B99" s="22"/>
-      <c r="C99" s="5" t="s">
+      <c r="D100" s="5"/>
+      <c r="E100" s="23"/>
+      <c r="F100" s="5"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="27"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" s="20"/>
-      <c r="B100" s="22"/>
-      <c r="C100" s="5" t="s">
+      <c r="D101" s="5"/>
+      <c r="E101" s="23"/>
+      <c r="F101" s="5"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="27"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101" s="20"/>
-      <c r="B101" s="22"/>
-      <c r="C101" s="5" t="s">
+      <c r="D102" s="5"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="5"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="27"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102" s="20"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="5" t="s">
+      <c r="D103" s="5"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="5"/>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="27"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103" s="20"/>
-      <c r="B103" s="22"/>
-      <c r="C103" s="5" t="s">
+      <c r="D104" s="5"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="5"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="27"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104" s="20"/>
-      <c r="B104" s="22"/>
-      <c r="C104" s="5" t="s">
+      <c r="D105" s="5"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="5"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="27"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105" s="20"/>
-      <c r="B105" s="22"/>
-      <c r="C105" s="5" t="s">
+      <c r="D106" s="5"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="5"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="27"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106" s="20"/>
-      <c r="B106" s="22"/>
-      <c r="C106" s="5" t="s">
+      <c r="D107" s="5"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="5"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="27"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107" s="20"/>
-      <c r="B107" s="22"/>
-      <c r="C107" s="5" t="s">
+      <c r="D108" s="5"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="5"/>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="27"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" s="20"/>
-      <c r="B108" s="22"/>
-      <c r="C108" s="5" t="s">
+      <c r="D109" s="5"/>
+      <c r="E109" s="23"/>
+      <c r="F109" s="5"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="27"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" s="20"/>
-      <c r="B109" s="22"/>
-      <c r="C109" s="5" t="s">
+      <c r="D110" s="5"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="5"/>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="27"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" s="20"/>
-      <c r="B110" s="22"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" s="20"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="5" t="s">
+      <c r="D111" s="5"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="5"/>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="27"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="22"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="5"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="27"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D111" s="10">
+      <c r="D113" s="10">
         <v>45896</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E113" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="F111" s="5"/>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" s="20"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5" t="s">
+      <c r="F113" s="5"/>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="27"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D112" s="10">
+      <c r="D114" s="10">
         <v>45871</v>
       </c>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="20"/>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="20" t="s">
+      <c r="E114" s="23"/>
+      <c r="F114" s="5"/>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="27"/>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="27" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="20"/>
-      <c r="C115" s="4" t="s">
+    <row r="117" spans="1:6">
+      <c r="A117" s="27"/>
+      <c r="C117" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E115" s="12">
+      <c r="E117" s="26">
         <v>45724</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="20"/>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="20"/>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="20"/>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="20" t="s">
+    <row r="118" spans="1:6">
+      <c r="A118" s="27"/>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="27"/>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="27"/>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="27" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="20"/>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="20"/>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="20"/>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="20"/>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="21" t="s">
+    <row r="122" spans="1:6">
+      <c r="A122" s="27"/>
+      <c r="C122" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E122" s="26">
+        <v>46004</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="27"/>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="27"/>
+      <c r="C124" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="E124" s="26">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="27"/>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="28" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="21"/>
-      <c r="C125" s="4" t="s">
+    <row r="127" spans="1:6">
+      <c r="A127" s="28"/>
+      <c r="C127" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E125" s="12">
+      <c r="E127" s="26">
         <v>45733</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="21"/>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="21"/>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="21"/>
+    <row r="128" spans="1:6">
+      <c r="A128" s="28"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="21" t="s">
+      <c r="A129" s="28"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="28"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="28" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="21"/>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="21"/>
-      <c r="C131" s="4" t="s">
+    <row r="132" spans="1:5">
+      <c r="A132" s="28"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="28"/>
+      <c r="C133" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="E131" s="12" t="s">
+      <c r="E133" s="26" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="21"/>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="21"/>
+    <row r="134" spans="1:5">
+      <c r="A134" s="28"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="A34:A81"/>
+    <mergeCell ref="A2:A35"/>
+    <mergeCell ref="A36:A83"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="B23:B27"/>
     <mergeCell ref="B28:B31"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A124:A128"/>
-    <mergeCell ref="A129:A133"/>
-    <mergeCell ref="A119:A123"/>
-    <mergeCell ref="B83:B110"/>
-    <mergeCell ref="A82:A113"/>
+    <mergeCell ref="A116:A120"/>
+    <mergeCell ref="A126:A130"/>
+    <mergeCell ref="A131:A135"/>
+    <mergeCell ref="A121:A125"/>
+    <mergeCell ref="B85:B112"/>
+    <mergeCell ref="A84:A115"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2498,13 +2589,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
     <col min="2" max="2" width="35.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.5" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.875" style="4" customWidth="1"/>
     <col min="6" max="16384" width="9" style="4"/>
   </cols>
@@ -2530,271 +2620,295 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="30" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="21"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="21"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="21"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="21"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="21"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="21"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="21"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="21"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="21"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="21"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="21"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="21"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="21"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="21"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="4">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E16" s="12">
+        <v>45999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="28"/>
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="21"/>
-      <c r="B17" s="4" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="28"/>
+      <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="21"/>
-      <c r="B18" s="4" t="s">
+    <row r="19" spans="1:5">
+      <c r="A19" s="28"/>
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="21"/>
-      <c r="B19" s="4" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="28"/>
+      <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="21"/>
-      <c r="B20" s="4" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="28"/>
+      <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="21"/>
-    </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="28"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="21"/>
-      <c r="B23" s="4" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="28"/>
+      <c r="B24" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="12">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="28"/>
+      <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="21"/>
-      <c r="B24" s="4" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="28"/>
+      <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="21"/>
-      <c r="B25" s="4" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="28"/>
+      <c r="B27" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="75">
-      <c r="A26" s="21"/>
-      <c r="B26" s="4" t="s">
+    <row r="28" spans="1:5" ht="75">
+      <c r="A28" s="28"/>
+      <c r="B28" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="21"/>
-      <c r="B27" s="4" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="28"/>
+      <c r="B29" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="21"/>
-      <c r="B28" s="4" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" s="28"/>
+      <c r="B30" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="21"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="21" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="28"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="21"/>
-      <c r="B31" s="4" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" s="28"/>
+      <c r="B33" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="21"/>
-      <c r="B32" s="4" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="28"/>
+      <c r="B34" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="21"/>
-      <c r="B33" s="4" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" s="28"/>
+      <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="21"/>
-      <c r="B34" s="4" t="s">
+    <row r="36" spans="1:5">
+      <c r="A36" s="28"/>
+      <c r="B36" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E36" s="12">
         <v>45970</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="21"/>
-      <c r="B35" s="4" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" s="28"/>
+      <c r="B37" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E37" s="12">
         <v>45959</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="21"/>
-      <c r="B36" s="4" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" s="28"/>
+      <c r="B38" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E38" s="12">
         <v>45964</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="21"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="21" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="28"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="21"/>
-      <c r="B39" s="4" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="28"/>
+      <c r="B41" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="37.5">
-      <c r="A40" s="21"/>
-      <c r="B40" s="13" t="s">
+    <row r="42" spans="1:5" ht="37.5">
+      <c r="A42" s="28"/>
+      <c r="B42" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E42" s="12">
         <v>45895</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="B41" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="12">
-        <v>45906</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="B42" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="12">
-        <v>45907</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43" s="12">
+        <v>45906</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="B44" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="12">
+        <v>45907</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="B45" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E45" s="12">
         <v>45957</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A2:A22"/>
+    <mergeCell ref="A23:A31"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A40:A42"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2832,15 +2946,15 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="30" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="21"/>
+      <c r="A3" s="28"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="21"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
@@ -2849,7 +2963,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="21"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="4" t="s">
         <v>149</v>
       </c>
@@ -2858,7 +2972,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="21"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="4" t="s">
         <v>147</v>
       </c>
@@ -2867,7 +2981,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="21"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="4" t="s">
         <v>148</v>
       </c>
@@ -2876,18 +2990,18 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="21"/>
+      <c r="A8" s="28"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="21"/>
+      <c r="A9" s="28"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="28" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="21"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="4" t="s">
         <v>150</v>
       </c>
@@ -2896,7 +3010,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="21"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="4" t="s">
         <v>151</v>
       </c>
@@ -2905,16 +3019,16 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="21"/>
+      <c r="A13" s="28"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="21"/>
+      <c r="A14" s="28"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="21"/>
+      <c r="A15" s="28"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="21"/>
+      <c r="A16" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3161,7 +3275,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>141</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -3172,7 +3286,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="21"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="4" t="s">
         <v>143</v>
       </c>
@@ -3181,10 +3295,10 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="21"/>
+      <c r="A5" s="28"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="21"/>
+      <c r="A6" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3220,21 +3334,21 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="21"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="21"/>
+      <c r="A5" s="28"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="21"/>
+      <c r="A6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="4" t="s">
